--- a/Donnees/Statistiques Démographiques et sociales/Démographie/Theme_Démographie (7).xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Démographie/Theme_Démographie (7).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Démographie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BEF8AA-D467-42B4-B976-F8AD2D9F3EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CBF149-744F-4831-802D-7EFDBBFBD830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1.1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="104">
   <si>
     <t>Tableau 1.1.1: Répartition de la population selon le milieu de résidence et le sexe; 1977 - 2027</t>
   </si>
@@ -135,9 +135,6 @@
     <t>Tableau 1.1.3 : Evolution de la population par groupe d'âge; 1977 - 2027</t>
   </si>
   <si>
-    <t>Groupe d'age</t>
-  </si>
-  <si>
     <t>0-4</t>
   </si>
   <si>
@@ -228,9 +225,6 @@
     <t>2023~Ensemble</t>
   </si>
   <si>
-    <t>Infantile (moins de 1an)</t>
-  </si>
-  <si>
     <t>Juvénile (1 à 4 ans)</t>
   </si>
   <si>
@@ -243,15 +237,9 @@
     <t>Tableau 1.1.4: Répartition(en %) de la population par groupe d'âge selon le sexe, en 2023</t>
   </si>
   <si>
-    <t>Groupe d'âge</t>
-  </si>
-  <si>
     <t>Sexe~Masculin</t>
   </si>
   <si>
-    <t>Sexe~Feminin</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -270,15 +258,6 @@
     <t>Tableau 1.1.6 : Répartition de la population par grands groupes d'âge selon le sexe, en 2023</t>
   </si>
   <si>
-    <t>0-14 ans</t>
-  </si>
-  <si>
-    <t>15-64 ans</t>
-  </si>
-  <si>
-    <t>65 ans et plus</t>
-  </si>
-  <si>
     <t>Tableau 1.1.7 : Principales caractéristiques démographiques de la population; 1977-2023</t>
   </si>
   <si>
@@ -306,30 +285,6 @@
     <t>Accroissement de la population~Taux d'accroissement intercensitaire (en %)</t>
   </si>
   <si>
-    <t>Population des groupes spécifiques(en%)~0 à 4 ans</t>
-  </si>
-  <si>
-    <t>Population des groupes spécifiques(en%)~6  11 ans</t>
-  </si>
-  <si>
-    <t>Population des groupes spécifiques(en%)~12  24 ans</t>
-  </si>
-  <si>
-    <t>Population des groupes spécifiques(en%)~ 0 à14 ans</t>
-  </si>
-  <si>
-    <t>Population des groupes spécifiques(en%)~15 à 24 ans</t>
-  </si>
-  <si>
-    <t>Population des groupes spécifiques(en%)~15 à59 ans</t>
-  </si>
-  <si>
-    <t>Population des groupes spécifiques(en%)~65 ans et plus</t>
-  </si>
-  <si>
-    <t>Population des groupes spécifiques(en%)~Femmes 15 à 49 ans</t>
-  </si>
-  <si>
     <t>Source : RGPH/1977-2023, MICS/2015 et EDSM/2019</t>
   </si>
   <si>
@@ -339,13 +294,52 @@
     <t>Wilaya~Hodh Charghi</t>
   </si>
   <si>
-    <t>Wilaya~Tiris-Zemmour</t>
-  </si>
-  <si>
     <t>Total~Masculine</t>
   </si>
   <si>
     <t>Total~Féminine</t>
+  </si>
+  <si>
+    <t>Groupe d'âge (années)</t>
+  </si>
+  <si>
+    <t>Sexe~Féminin</t>
+  </si>
+  <si>
+    <t>0-14</t>
+  </si>
+  <si>
+    <t>15-64</t>
+  </si>
+  <si>
+    <t>65+</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques (en %)~0-4 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques (en %)~6-11 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques (en %)~12-24 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques (en %)~ 0-14 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques (en %)~15-24 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques (en %)~15-59 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques (en %)~Femmes 15-49 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques (en %)~65 ans +</t>
+  </si>
+  <si>
+    <t>Infantile (moins de 1 an)</t>
   </si>
 </sst>
 </file>
@@ -749,7 +743,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>1338830</v>
@@ -781,7 +775,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="B4">
         <v>658361</v>
@@ -813,7 +807,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B5">
         <v>680469</v>
@@ -1090,7 +1084,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>1338830</v>
@@ -1611,7 +1605,7 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="75.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.35">
@@ -1621,7 +1615,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -1653,7 +1647,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>1338830</v>
@@ -1685,7 +1679,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>216787</v>
@@ -1717,7 +1711,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>219206</v>
@@ -1749,7 +1743,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>152665</v>
@@ -1781,7 +1775,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>138274</v>
@@ -1813,7 +1807,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>111318</v>
@@ -1845,7 +1839,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>89029</v>
@@ -1877,7 +1871,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>73724</v>
@@ -1909,7 +1903,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>61709</v>
@@ -1941,7 +1935,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>68686</v>
@@ -1973,7 +1967,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>47843</v>
@@ -2005,7 +1999,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>47120</v>
@@ -2037,7 +2031,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>34398</v>
@@ -2069,7 +2063,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>27262</v>
@@ -2101,7 +2095,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>14572</v>
@@ -2133,7 +2127,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>18414</v>
@@ -2165,7 +2159,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19">
         <v>17823</v>
@@ -2211,30 +2205,31 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="93.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -2248,7 +2243,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0.1502</v>
@@ -2262,7 +2257,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0.14649999999999999</v>
@@ -2276,7 +2271,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>0.13739999999999999</v>
@@ -2290,7 +2285,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>0.115</v>
@@ -2304,7 +2299,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>7.9699999999999993E-2</v>
@@ -2318,7 +2313,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>6.4199999999999993E-2</v>
@@ -2332,7 +2327,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>5.5899999999999998E-2</v>
@@ -2346,7 +2341,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>4.8300000000000003E-2</v>
@@ -2360,7 +2355,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>4.1200000000000001E-2</v>
@@ -2374,7 +2369,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>3.5999999999999997E-2</v>
@@ -2388,7 +2383,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>3.2000000000000001E-2</v>
@@ -2402,7 +2397,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>2.7400000000000001E-2</v>
@@ -2416,7 +2411,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>2.2800000000000001E-2</v>
@@ -2430,7 +2425,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>1.7500000000000002E-2</v>
@@ -2444,7 +2439,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>1.18E-2</v>
@@ -2458,7 +2453,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B19">
         <v>5.8999999999999999E-3</v>
@@ -2472,7 +2467,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B20">
         <v>8.0999999999999996E-3</v>
@@ -2486,7 +2481,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2506,26 +2501,26 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>2375470</v>
@@ -2539,7 +2534,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>356790</v>
@@ -2553,7 +2548,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>348088</v>
@@ -2567,7 +2562,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>326371</v>
@@ -2581,7 +2576,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>273104</v>
@@ -2595,7 +2590,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>189243</v>
@@ -2609,7 +2604,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>152472</v>
@@ -2623,7 +2618,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>132832</v>
@@ -2637,7 +2632,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>114823</v>
@@ -2651,7 +2646,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>97811</v>
@@ -2665,7 +2660,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>85511</v>
@@ -2679,7 +2674,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>75993</v>
@@ -2693,7 +2688,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>65195</v>
@@ -2707,7 +2702,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>54193</v>
@@ -2721,7 +2716,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>41572</v>
@@ -2735,7 +2730,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>28133</v>
@@ -2749,7 +2744,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B19">
         <v>14118</v>
@@ -2763,7 +2758,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B20">
         <v>19220</v>
@@ -2777,7 +2772,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2791,30 +2786,32 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>2375470</v>
@@ -2828,7 +2825,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B4">
         <v>1031249</v>
@@ -2842,7 +2839,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B5">
         <v>1241178</v>
@@ -2856,7 +2853,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B6">
         <v>103043</v>
@@ -2870,7 +2867,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2888,7 +2885,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2906,10 +2903,10 @@
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>5</v>
@@ -2917,7 +2914,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>6.3</v>
@@ -2940,7 +2937,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B4">
         <v>49</v>
@@ -2966,7 +2963,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D5">
         <v>56.9</v>
@@ -2983,7 +2980,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D6">
         <v>58.6</v>
@@ -3000,7 +2997,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B7">
         <v>40</v>
@@ -3023,7 +3020,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>2.93</v>
@@ -3046,7 +3043,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B9">
         <v>16.190000000000001</v>
@@ -3072,7 +3069,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>16.8</v>
@@ -3089,7 +3086,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>28.4</v>
@@ -3106,7 +3103,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B12">
         <v>43.97</v>
@@ -3132,7 +3129,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B13">
         <v>18.600000000000001</v>
@@ -3158,7 +3155,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B14">
         <v>50.2</v>
@@ -3184,7 +3181,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B15">
         <v>3.8</v>
@@ -3210,7 +3207,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B16">
         <v>44</v>
@@ -3236,7 +3233,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3254,7 +3251,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -3266,7 +3263,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -3274,7 +3271,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -3291,7 +3288,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B4">
         <v>5.0999999999999996</v>
@@ -3461,7 +3458,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>4.3</v>
@@ -3545,7 +3542,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3563,53 +3560,53 @@
   <sheetData>
     <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="B3">
         <v>66</v>
@@ -3650,7 +3647,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B4">
         <v>43</v>
@@ -3691,7 +3688,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5">
         <v>106</v>
@@ -3732,7 +3729,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Donnees/Statistiques Démographiques et sociales/Démographie/Theme_Démographie (7).xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Démographie/Theme_Démographie (7).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Démographie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CBF149-744F-4831-802D-7EFDBBFBD830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACAE66B-12FF-4726-BC7D-731021E3C932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1.1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="T1.8" sheetId="9" r:id="rId8"/>
     <sheet name="T1.9" sheetId="4" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -2201,19 +2202,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="93.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>90</v>
       </c>
@@ -2227,200 +2228,203 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>70</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4">
-        <v>0.1502</v>
+        <v>15.02</v>
       </c>
       <c r="C4">
-        <v>0.13519999999999999</v>
+        <v>13.52</v>
       </c>
       <c r="D4">
-        <v>0.14249999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>14.249999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>36</v>
       </c>
       <c r="B5">
-        <v>0.14649999999999999</v>
+        <v>14.649999999999999</v>
       </c>
       <c r="C5">
-        <v>0.13389999999999999</v>
+        <v>13.389999999999999</v>
       </c>
       <c r="D5">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>14.000000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>37</v>
       </c>
       <c r="B6">
-        <v>0.13739999999999999</v>
+        <v>13.74</v>
       </c>
       <c r="C6">
-        <v>0.12859999999999999</v>
+        <v>12.86</v>
       </c>
       <c r="D6">
-        <v>0.1328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>38</v>
       </c>
       <c r="B7">
-        <v>0.115</v>
+        <v>11.5</v>
       </c>
       <c r="C7">
-        <v>0.11360000000000001</v>
+        <v>11.360000000000001</v>
       </c>
       <c r="D7">
-        <v>0.1143</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>11.43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
       <c r="B8">
-        <v>7.9699999999999993E-2</v>
+        <v>7.9699999999999989</v>
       </c>
       <c r="C8">
-        <v>9.06E-2</v>
+        <v>9.06</v>
       </c>
       <c r="D8">
-        <v>8.5400000000000004E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8.5400000000000009</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
       <c r="B9">
-        <v>6.4199999999999993E-2</v>
+        <v>6.419999999999999</v>
       </c>
       <c r="C9">
-        <v>7.6700000000000004E-2</v>
+        <v>7.6700000000000008</v>
       </c>
       <c r="D9">
-        <v>7.0699999999999999E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7.07</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>41</v>
       </c>
       <c r="B10">
-        <v>5.5899999999999998E-2</v>
+        <v>5.59</v>
       </c>
       <c r="C10">
-        <v>6.5799999999999997E-2</v>
+        <v>6.58</v>
       </c>
       <c r="D10">
-        <v>6.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>42</v>
       </c>
       <c r="B11">
-        <v>4.8300000000000003E-2</v>
+        <v>4.83</v>
       </c>
       <c r="C11">
-        <v>5.5199999999999999E-2</v>
+        <v>5.52</v>
       </c>
       <c r="D11">
-        <v>5.1900000000000002E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>43</v>
       </c>
       <c r="B12">
-        <v>4.1200000000000001E-2</v>
+        <v>4.12</v>
       </c>
       <c r="C12">
-        <v>4.36E-2</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="D12">
-        <v>4.24E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4.24</v>
+      </c>
+      <c r="G12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>44</v>
       </c>
       <c r="B13">
-        <v>3.5999999999999997E-2</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C13">
-        <v>3.6600000000000001E-2</v>
+        <v>3.66</v>
       </c>
       <c r="D13">
-        <v>3.6299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>45</v>
       </c>
       <c r="B14">
-        <v>3.2000000000000001E-2</v>
+        <v>3.2</v>
       </c>
       <c r="C14">
-        <v>3.2300000000000002E-2</v>
+        <v>3.2300000000000004</v>
       </c>
       <c r="D14">
-        <v>3.2099999999999997E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3.2099999999999995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>46</v>
       </c>
       <c r="B15">
-        <v>2.7400000000000001E-2</v>
+        <v>2.74</v>
       </c>
       <c r="C15">
-        <v>2.6800000000000001E-2</v>
+        <v>2.68</v>
       </c>
       <c r="D15">
-        <v>2.7099999999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>47</v>
       </c>
       <c r="B16">
-        <v>2.2800000000000001E-2</v>
+        <v>2.2800000000000002</v>
       </c>
       <c r="C16">
-        <v>2.1100000000000001E-2</v>
+        <v>2.11</v>
       </c>
       <c r="D16">
-        <v>2.1899999999999999E-2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -2428,13 +2432,13 @@
         <v>48</v>
       </c>
       <c r="B17">
-        <v>1.7500000000000002E-2</v>
+        <v>1.7500000000000002</v>
       </c>
       <c r="C17">
-        <v>1.5800000000000002E-2</v>
+        <v>1.58</v>
       </c>
       <c r="D17">
-        <v>1.66E-2</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -2442,13 +2446,13 @@
         <v>49</v>
       </c>
       <c r="B18">
-        <v>1.18E-2</v>
+        <v>1.18</v>
       </c>
       <c r="C18">
-        <v>1.0500000000000001E-2</v>
+        <v>1.05</v>
       </c>
       <c r="D18">
-        <v>1.12E-2</v>
+        <v>1.1199999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2456,13 +2460,13 @@
         <v>71</v>
       </c>
       <c r="B19">
-        <v>5.8999999999999999E-3</v>
+        <v>0.59</v>
       </c>
       <c r="C19">
-        <v>5.4000000000000003E-3</v>
+        <v>0.54</v>
       </c>
       <c r="D19">
-        <v>5.7000000000000002E-3</v>
+        <v>0.57000000000000006</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -2470,13 +2474,13 @@
         <v>72</v>
       </c>
       <c r="B20">
-        <v>8.0999999999999996E-3</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="C20">
-        <v>8.0999999999999996E-3</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="D20">
-        <v>8.0999999999999996E-3</v>
+        <v>0.80999999999999994</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
